--- a/token_metrics/linda_1/delta_mode_1/eval_linda_delta1.xlsx
+++ b/token_metrics/linda_1/delta_mode_1/eval_linda_delta1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Università - Borsa di Ricerca\HDT Framework Repo\HumanDigitalTwin\token_metrics\linda_1\delta_mode_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246229F5-7E51-442C-814D-AF90326D4875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE841A56-0FB9-41F4-9719-26606E102E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2716,7 +2716,7 @@
         <v>181</v>
       </c>
       <c r="B5">
-        <v>147</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
